--- a/out/bench/results.xlsx
+++ b/out/bench/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1154,6 +1154,491 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>cert_only (только правила CERT C)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>эскалация</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="K17" t="n">
+        <v>150</v>
+      </c>
+      <c r="L17" t="n">
+        <v>448513</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ступень 1 каскада; лучшая одноступенчатая переносимая</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>cwe_only (только карточки CWE)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>150</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>конфигурация A (CWE+CERT+flawfinder)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>эскалация</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="K19" t="n">
+        <v>150</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>склейка трёх блоков хуже одного</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>каскад cert_only + ступень 2 голосование k&gt;=3/5</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>150</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>ЛУЧШЕЕ переносимое; корпус не нужен</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>каскад ступень 2 вариант A (k=1)</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>150</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>голосование лучше одиночного вызова</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>критик поверх рассуждения ступени 1 (все 150)</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>150</v>
+      </c>
+      <c r="L22" t="n">
+        <v>432770</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>тупик: критик рушит recall</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>критик только по корзине uncertain</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>150</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>не лучше каскада</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>суд прокурор+защита+судья</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.0755</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="n">
+        <v>150</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2440442</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>тупик: защита обнуляет recall</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>офлайн</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>детекторы v2</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>регулярки после починки</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>200</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>ipv6/api_key/time/credit_card; проверено и на n=500</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>только LLM после починки типов</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9295</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="n">
+        <v>200</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>разметка типа исправлена</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>гибрид</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>детекторы v2 + LLM после починки</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>200</v>
+      </c>
+      <c r="L27" t="n">
+        <v>566542</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>детекторы в промежуточном состоянии, нужен чистый пересчёт</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/bench/results.xlsx
+++ b/out/bench/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1532,13 +1532,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.965</v>
+        <v>0.9664</v>
       </c>
       <c r="F25" t="n">
-        <v>0.471</v>
+        <v>0.4723</v>
       </c>
       <c r="G25" t="n">
-        <v>0.633</v>
+        <v>0.6345</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>ipv6/api_key/time/credit_card; проверено и на n=500</t>
+          <t>ipv6/api_key/time/credit_card/account_number/national_id</t>
         </is>
       </c>
     </row>
@@ -1612,17 +1612,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>детекторы v2 + LLM после починки</t>
+          <t>детекторы v2 + LLM (актуальное)</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.918</v>
+        <v>0.9543</v>
       </c>
       <c r="F27" t="n">
-        <v>0.876</v>
+        <v>0.8894</v>
       </c>
       <c r="G27" t="n">
-        <v>0.897</v>
+        <v>0.9207</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -1635,7 +1635,138 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>детекторы в промежуточном состоянии, нужен чистый пересчёт</t>
+          <t>чистый пересчёт; на n=500 F1 0.903</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>объединение скринера и cert_only</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="n">
+        <v>150</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>тупик: запас комбинации — одна уязвимость из 50</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ступень 2 расширена на корзину secure</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="n">
+        <v>150</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>тупик: 0 изменённых вердиктов при k&gt;=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>офлайн</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>TF-IDF+LogReg+структурные признаки</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>против маскировки</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9876</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.9848</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>+0.0004 F1 — смена признаков не окупается</t>
         </is>
       </c>
     </row>

--- a/out/bench/results.xlsx
+++ b/out/bench/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,16 +503,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.538</v>
+        <v>0.5385</v>
       </c>
       <c r="F2" t="n">
-        <v>0.14</v>
+        <v>0.1522</v>
       </c>
       <c r="G2" t="n">
-        <v>0.222</v>
+        <v>0.2373</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06</v>
+        <v>0.0577</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.643</v>
+        <v>0.6429</v>
       </c>
       <c r="F3" t="n">
-        <v>0.18</v>
+        <v>0.1957</v>
       </c>
       <c r="G3" t="n">
-        <v>0.281</v>
+        <v>0.3</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05</v>
+        <v>0.0481</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.6087</v>
       </c>
       <c r="F4" t="n">
-        <v>0.36</v>
+        <v>0.3043</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5</v>
+        <v>0.4058</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -650,16 +650,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.929</v>
+        <v>0.7692</v>
       </c>
       <c r="F5" t="n">
-        <v>0.26</v>
+        <v>0.2174</v>
       </c>
       <c r="G5" t="n">
-        <v>0.406</v>
+        <v>0.339</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01</v>
+        <v>0.0288</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -671,7 +671,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>CV дала F1 0.25 — разрыв не объяснён</t>
+          <t>порог 0.5943 подобран 5-fold CV на пуле без eval150</t>
         </is>
       </c>
     </row>
@@ -694,13 +694,17 @@
           <t>статический анализатор</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>0.6429</v>
+      </c>
       <c r="F6" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
+        <v>0.1957</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3</v>
+      </c>
       <c r="H6" t="n">
-        <v>0.05</v>
+        <v>0.0481</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -735,12 +739,18 @@
           <t>регулярки</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>0.1382</v>
+      </c>
       <c r="F7" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+        <v>0.0919</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.1104</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.034</v>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
@@ -786,7 +796,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.667</v>
+        <v>0.6933</v>
       </c>
       <c r="K8" t="n">
         <v>150</v>
@@ -1174,16 +1184,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.656</v>
+        <v>0.6562</v>
       </c>
       <c r="F17" t="n">
-        <v>0.42</v>
+        <v>0.4565</v>
       </c>
       <c r="G17" t="n">
-        <v>0.512</v>
+        <v>0.5385</v>
       </c>
       <c r="H17" t="n">
-        <v>0.11</v>
+        <v>0.1058</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1225,16 +1235,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.6</v>
+        <v>0.5667</v>
       </c>
       <c r="F18" t="n">
-        <v>0.36</v>
+        <v>0.3696</v>
       </c>
       <c r="G18" t="n">
-        <v>0.45</v>
+        <v>0.4474</v>
       </c>
       <c r="H18" t="n">
-        <v>0.12</v>
+        <v>0.125</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
@@ -1267,13 +1277,13 @@
         <v>0.5</v>
       </c>
       <c r="F19" t="n">
-        <v>0.26</v>
+        <v>0.2826</v>
       </c>
       <c r="G19" t="n">
-        <v>0.342</v>
+        <v>0.3611</v>
       </c>
       <c r="H19" t="n">
-        <v>0.13</v>
+        <v>0.125</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1313,16 +1323,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.676</v>
+        <v>0.6486</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>0.575</v>
+        <v>0.5783</v>
       </c>
       <c r="H20" t="n">
-        <v>0.12</v>
+        <v>0.125</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
@@ -1359,13 +1369,13 @@
         <v>0.575</v>
       </c>
       <c r="F21" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="G21" t="n">
-        <v>0.511</v>
+        <v>0.5349</v>
       </c>
       <c r="H21" t="n">
-        <v>0.17</v>
+        <v>0.1635</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
@@ -1402,13 +1412,13 @@
         <v>0.5</v>
       </c>
       <c r="F22" t="n">
-        <v>0.18</v>
+        <v>0.1957</v>
       </c>
       <c r="G22" t="n">
-        <v>0.265</v>
+        <v>0.2812</v>
       </c>
       <c r="H22" t="n">
-        <v>0.09</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
@@ -1444,16 +1454,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.59</v>
+        <v>0.5897</v>
       </c>
       <c r="F23" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="G23" t="n">
-        <v>0.517</v>
+        <v>0.5412</v>
       </c>
       <c r="H23" t="n">
-        <v>0.16</v>
+        <v>0.1538</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
@@ -1487,16 +1497,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.667</v>
+        <v>0.6667</v>
       </c>
       <c r="F24" t="n">
-        <v>0.04</v>
+        <v>0.0435</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0755</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>0.01</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
@@ -1659,16 +1669,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5641</v>
       </c>
       <c r="F28" t="n">
-        <v>0.44</v>
+        <v>0.4783</v>
       </c>
       <c r="G28" t="n">
-        <v>0.494</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>0.17</v>
+        <v>0.1635</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
@@ -1702,16 +1712,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.676</v>
+        <v>0.6486</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>0.575</v>
+        <v>0.5783</v>
       </c>
       <c r="H29" t="n">
-        <v>0.12</v>
+        <v>0.125</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
@@ -1770,6 +1780,1108 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>офлайн</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>logreg TF-IDF</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>полный корпус, 5-fold OOF</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.2647</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.3981</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.0655</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>18864</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>ДИАГНОСТИКА: нужен размеченный корпус; база 5.59%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>офлайн</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>logreg TF-IDF</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>полный корпус, 5-fold OOF, порог 0.5583</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="n">
+        <v>18864</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>порог подобран на тех же OOF — слегка оптимистично</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>офлайн</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>flawfinder</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>полный корпус</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.1148</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.1668</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.0762</v>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="n">
+        <v>18864</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>классический SAST на всём корпусе</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>3</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>qwen3-30b-a3b</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>базовый промпт</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>эскалация</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="K34" t="n">
+        <v>150</v>
+      </c>
+      <c r="L34" t="n">
+        <v>433872</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>OpenRouter, $0.0058</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>3</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>openai/gpt-5-nano</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>базовый промпт</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.457</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>эскалация</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="K35" t="n">
+        <v>150</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1105990</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>OpenRouter, $0.3362</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>3</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>openai/gpt-5-mini</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>базовый промпт</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>эскалация</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="K36" t="n">
+        <v>150</v>
+      </c>
+      <c r="L36" t="n">
+        <v>595043</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>OpenRouter, $0.6627</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>3</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>deepseek-chat (OpenRouter)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>базовый промпт</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>эскалация</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K37" t="n">
+        <v>150</v>
+      </c>
+      <c r="L37" t="n">
+        <v>338740</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>OpenRouter, $0.1121</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>3</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>GigaChat-3-Ultra</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>базовый промпт</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>эскалация</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="K38" t="n">
+        <v>150</v>
+      </c>
+      <c r="L38" t="n">
+        <v>127312</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>GigaChat, бесплатно</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>3</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>GigaChat-2</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>базовый промпт</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>эскалация</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="K39" t="n">
+        <v>150</v>
+      </c>
+      <c r="L39" t="n">
+        <v>106367</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>GigaChat, бесплатно</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>3</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>GigaChat-2-Pro</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>базовый промпт</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>эскалация</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="K40" t="n">
+        <v>150</v>
+      </c>
+      <c r="L40" t="n">
+        <v>135024</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>GigaChat, бесплатно</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>гибрид</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>GigaChat-3-Ultra</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>офлайн+серая зона</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9944</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.9724</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.9833</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>LLM решает только серую зону (~45 из 1000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>гибрид</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>openai/gpt-5-mini</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>офлайн+серая зона</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.9962</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.9706</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.9832</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>LLM решает только серую зону (~45 из 1000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>гибрид</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>qwen3-30b-a3b</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>офлайн+серая зона</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.9888</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.9724</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.9805</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>LLM решает только серую зону (~45 из 1000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>гибрид</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>deepseek-chat (OpenRouter)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>офлайн+серая зона</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0.9906</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.9688</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.9796</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>LLM решает только серую зону (~45 из 1000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>гибрид</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>GigaChat-2-Pro</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>офлайн+серая зона</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.9925</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.9669</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.9795</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>LLM решает только серую зону (~45 из 1000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>гибрид</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>GigaChat-2</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>офлайн+серая зона</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9923999999999999</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.9631999999999999</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.9776</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>LLM решает только серую зону (~45 из 1000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>гибрид</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>openai/gpt-5-nano</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>офлайн+серая зона</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9962</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.9596</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.9775</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>LLM решает только серую зону (~45 из 1000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>3</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>базовый промпт (набор 600)</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="n">
+        <v>600</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1246642</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>перезамер 27.08 вечер; набор case3_eval600_ids.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>3</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>cert_only (набор 600)</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>эскалация</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K49" t="n">
+        <v>600</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>ЛУЧШЕЕ по кейсу 3; 1 вызов на фрагмент</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>3</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>каскад cert_only + голосование k&gt;=3/5 (набор 600)</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="n">
+        <v>600</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>ступень 2 даёт +0.004 при σ 0.03 — не окупается</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>гибрид</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>qwen/qwen3-30b-a3b (OR)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>детекторы v2 + LLM</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="n">
+        <v>200</v>
+      </c>
+      <c r="L51" t="n">
+        <v>653321</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>только LLM 0.521; $0.019 — самый дешёвый</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>гибрид</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>deepseek/deepseek-chat (OR)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>детекторы v2 + LLM</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="n">
+        <v>200</v>
+      </c>
+      <c r="L52" t="n">
+        <v>568732</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>только LLM 0.571; $0.084 — лучший баланс</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>гибрид</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>openai/gpt-5-nano</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>детекторы v2 + LLM</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="n">
+        <v>200</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1414382</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>только LLM 0.565; $0.194; 2259 completion-ток/док</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>гибрид</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>openai/gpt-5-mini</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>детекторы v2 + LLM</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.901</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="n">
+        <v>200</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1034072</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>только LLM 0.553; $0.587 — дороже всех и хуже deepseek</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/bench/results.xlsx
+++ b/out/bench/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2882,6 +2882,408 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>3</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>cert_only (набор 600; контроль пересборки)</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="n">
+        <v>600</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1867000</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>воспроизведено из каскадных артефактов; база сравнения сессии 28.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>3</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>cert_only с чтением uncertain как vulnerable (0 вызовов)</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>тривиальный «всё уязвимо» F1</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K56" t="n">
+        <v>600</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>ХУЖЕ тривиального базлайна — корзина uncertain информации не несёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>3</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>форсированно бинарный cert_only (1 вызов)</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>нарушений бинарной инструкции</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>600</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1820013</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>recall падает вдвое: без права на «не уверен» модель уходит в secure</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>3</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>qwen/qwen3-30b-a3b (OR)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>cert_only (набор 600)</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>CWE accuracy</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="K58" t="n">
+        <v>600</v>
+      </c>
+      <c r="L58" t="n">
+        <v>2562146</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>хуже deepseek на 0.141 (4.7σ) и дороже прайса: 4270 ток/фрагмент</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>3</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ablation: sensitive_none (блока знаний нет)</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>длина блока симв</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>600</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1779000</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>контроль снизу для развилки по блоку знаний</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>3</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ablation: decoy_style (правила оформления кода)</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>длина блока симв</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>510</v>
+      </c>
+      <c r="K60" t="n">
+        <v>600</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1779000</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>нерелевантный чек-лист неотличим от CERT в пределах σ</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>3</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ablation: nudge_only (одна фраза без правил)</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>длина блока симв</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>60</v>
+      </c>
+      <c r="K61" t="n">
+        <v>600</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1779000</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>одна фраза воспроизводит эффект блока CERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>3</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ablation: cert_hardcoded (константа CERT)</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>длина блока симв</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>510</v>
+      </c>
+      <c r="K62" t="n">
+        <v>600</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1779000</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>зашитая строка = «динамический» cert_only (0.386): retrieval отсутствует</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/bench/results.xlsx
+++ b/out/bench/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3284,6 +3284,96 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>3</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>deepseek/deepseek-chat (OR)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>nudge_only — контроль на OpenRouter (1 вызов)</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="n">
+        <v>600</v>
+      </c>
+      <c r="L63" t="n">
+        <v>2008000</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>контроль для декомпозиции; на прямом API та же конфигурация дала 0.349</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>3</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>deepseek/deepseek-chat (OR)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>декомпозиция рассуждения до вердикта (2 вызова)</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="n">
+        <v>600</v>
+      </c>
+      <c r="L64" t="n">
+        <v>2009000</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>-0.002 к контролю при σ 0.03 — ноль; предложение 3 из case3_knowledge_sources закрыто</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/bench/results.xlsx
+++ b/out/bench/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3374,6 +3374,237 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>3</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>дообученная модель</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>mahdin70/CodeBERT-PrimeVul-BigVul</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>порог по умолчанию 0.5</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>утечка в train доля</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="K65" t="n">
+        <v>600</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>локальный CPU-инференс; вровень с нашей LLM 0.386 при совсем ином рабочем режиме</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>3</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>дообученная модель</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>mahdin70/CodeBERT-PrimeVul-BigVul</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>порог подобран под FPR 0.128</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>утечка в train доля</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="K66" t="n">
+        <v>600</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>порог подобран ПО НАШИМ ЖЕ ЛЕЙБЛАМ — читать с оговоркой</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>3</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>дообученная модель</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>mahdin70/CodeBERT-PrimeVul-BigVul</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>на 227 УТЁКШИХ фрагментах (FPR-порог)</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="n">
+        <v>227</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>запоминание: модель обучалась на этих же фрагментах</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>3</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>дообученная модель</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>mahdin70/CodeBERT-PrimeVul-BigVul</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>на 373 ЧИСТЫХ фрагментах (FPR-порог)</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="n">
+        <v>373</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>честное сравнение; σ(F1) около 0.045 на этом подмножестве</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>3</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>cert_only на тех же 373 чистых фрагментах</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="n">
+        <v>373</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>наша поставка на сопоставимом подмножестве: разрыв 0.097 ≈ 2σ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/bench/results.xlsx
+++ b/out/bench/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3605,6 +3605,92 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>1</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>инфраструктура</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>deepseek-chat (прямой API)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>кеш префикса: текущий порядок блоков промпта</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>доля попаданий (устоявшаяся)</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="K70" t="n">
+        <v>60</v>
+      </c>
+      <c r="L70" t="n">
+        <v>85987</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>кешируется ~640 ток/док; переменный блок «Контекст документа» отсекает константные Правила</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>1</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>инфраструктура</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>deepseek-chat (прямой API)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>кеш префикса: блок «Контекст документа» перенесён вниз</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>доля попаданий (устоявшаяся)</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="K71" t="n">
+        <v>60</v>
+      </c>
+      <c r="L71" t="n">
+        <v>85964</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>кешируется ровно 1024 ток/док; miss на документ 757 -&gt; 387 (-49%); F1 на этом порядке НЕ пересчитан</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/bench/results.xlsx
+++ b/out/bench/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3691,6 +3691,104 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>1</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>гибрид</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>детекторы v2 + LLM, блок «Контекст документа» перенесён вниз</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0.9512</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.8888</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.9189000000000001</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>кеш префикса (живой)</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="K72" t="n">
+        <v>200</v>
+      </c>
+      <c r="L72" t="n">
+        <v>566898</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>перестановка применена в llm_layer.py; F1 −0.002 к 0.9207 на тех же 200 документах</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>1</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>гибрид</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>то же, независимая проверка n=500 seed 7</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0.9286</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.8705000000000001</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.8986</v>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>кеш префикса (живой)</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="K73" t="n">
+        <v>500</v>
+      </c>
+      <c r="L73" t="n">
+        <v>1414390</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>−0.004 к 0.9030 на старом порядке; обе дельты в шуме</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/bench/results.xlsx
+++ b/out/bench/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3789,6 +3789,178 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>гибрид (боевой прогон)</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>deepseek-chat (прямой API)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>офлайн TF-IDF+LogReg порог 0.80 + LLM серой зоны, весь test</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>вызовов LLM</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>480</v>
+      </c>
+      <c r="K74" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L74" t="n">
+        <v>493678</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>боевая выгрузка out/case2_verdicts.xlsx; 4.8% потока ушло в LLM; серая зона помечена «отправить на ручную проверку» по требованию ТЗ</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>3</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>cert_only (боевой прогон)</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>deepseek-chat (прямой API)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>весь корпус, max_tokens 2048 + эскалация лимита на обрывах</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>доля vulnerable</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>0.1512</v>
+      </c>
+      <c r="K75" t="n">
+        <v>18864</v>
+      </c>
+      <c r="L75" t="n">
+        <v>54679350</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>боевая выгрузка out/case3_verdicts.xlsx; 2853 vulnerable / 5147 secure / 10864 uncertain; 0 заглушек; кеш префикса 0.705</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>3</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>добор обрывов</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>deepseek-chat (прямой API)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>137 фрагментов на max_tokens 4096 + 5 на 8192</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>из них vulnerable</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>120</v>
+      </c>
+      <c r="K76" t="n">
+        <v>142</v>
+      </c>
+      <c r="L76" t="n">
+        <v>1237717</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>обрыв на max_tokens бил избирательно по уязвимым: 130 из 137 — Unterminated string на поле patched_code; без добора терялось 4.2% находок</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>1</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>гибрид (боевой прогон)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>deepseek-chat (прямой API)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>детекторы v2 + LLM, весь test, doc_id разведён по вхождениям uid</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>док-в на ручную проверку</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>2067</v>
+      </c>
+      <c r="K77" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L77" t="n">
+        <v>143211997</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>боевая выгрузка out/case1_verdicts.xlsx; 615620 замен; true_leak&gt;0 у 24 док-в из 100000; кеш префикса 0.771</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/bench/results.xlsx
+++ b/out/bench/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3961,6 +3961,208 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>1</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>гибрид (замер сдачи)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>deepseek-chat (прямой API)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>span-exact на ВСЕЙ доставленной выгрузке, 100 000 док</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0.9301</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.8682</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.8981</v>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>recall без учёта типа</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>0.9088000000000001</v>
+      </c>
+      <c r="K78" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L78" t="n">
+        <v>143211997</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>850 340 золотых спанов; n=500 предсказала точно (0.8986), n=200 была оптимистична на +0.023</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>гибрид (замер сдачи)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>deepseek-chat (прямой API)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>офлайн 0.80 + LLM серой зоны, весь test</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0.9817</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.9875</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>MCC</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>0.9661</v>
+      </c>
+      <c r="K79" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L79" t="n">
+        <v>493678</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>на серой зоне 480 док LLM верно решил 367 против 366 у офлайна — прирост ОДИН документ</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>2</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>только офлайн (контроль)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>TF-IDF+LogReg</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>без LLM вовсе, весь test</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0.9871</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.9818</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.9844000000000001</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.0154</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>MCC</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>0.966</v>
+      </c>
+      <c r="K80" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>F1 −0.0002 к гибриду и FPR ЛУЧШЕ; прежний прирост гибрида 0.989 против 0.984 был шумом n=1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>3</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>cert_only (замер сдачи)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>deepseek-chat (прямой API)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>весь корпус против v4-разметки, доля уязвимых 5.6%</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0.1052</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.1535</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.1434</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Youden J</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="K81" t="n">
+        <v>18864</v>
+      </c>
+      <c r="L81" t="n">
+        <v>54679350</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>J 0.141 против 0.140 на eval600 — различающая способность та же, F1 упал только от доли классов; тривиальное «всё vulnerable» даёт 0.1059</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/bench/results.xlsx
+++ b/out/bench/results.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,8 +519,10 @@
           <t>эскалация</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>0.233</v>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.233</t>
+        </is>
       </c>
       <c r="K2" t="n">
         <v>150</v>
@@ -570,8 +572,10 @@
           <t>эскалация</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>0.02</v>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
       </c>
       <c r="K3" t="n">
         <v>150</v>
@@ -795,8 +799,10 @@
           <t>accuracy</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>0.6933</v>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.6933</t>
+        </is>
       </c>
       <c r="K8" t="n">
         <v>150</v>
@@ -1053,8 +1059,10 @@
           <t>acc серой зоны</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>0.8179999999999999</v>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.818</t>
+        </is>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -1104,8 +1112,10 @@
           <t>acc серой зоны</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v>0.591</v>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.591</t>
+        </is>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -1200,8 +1210,10 @@
           <t>эскалация</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v>0.593</v>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.593</t>
+        </is>
       </c>
       <c r="K17" t="n">
         <v>150</v>
@@ -1290,8 +1302,10 @@
           <t>эскалация</t>
         </is>
       </c>
-      <c r="J19" t="n">
-        <v>0.547</v>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.547</t>
+        </is>
       </c>
       <c r="K19" t="n">
         <v>150</v>
@@ -1951,8 +1965,10 @@
           <t>эскалация</t>
         </is>
       </c>
-      <c r="J34" t="n">
-        <v>0.107</v>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0.107</t>
+        </is>
       </c>
       <c r="K34" t="n">
         <v>150</v>
@@ -2002,8 +2018,10 @@
           <t>эскалация</t>
         </is>
       </c>
-      <c r="J35" t="n">
-        <v>0.147</v>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0.147</t>
+        </is>
       </c>
       <c r="K35" t="n">
         <v>150</v>
@@ -2053,8 +2071,10 @@
           <t>эскалация</t>
         </is>
       </c>
-      <c r="J36" t="n">
-        <v>0.573</v>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0.573</t>
+        </is>
       </c>
       <c r="K36" t="n">
         <v>150</v>
@@ -2104,8 +2124,10 @@
           <t>эскалация</t>
         </is>
       </c>
-      <c r="J37" t="n">
-        <v>0.28</v>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
       </c>
       <c r="K37" t="n">
         <v>150</v>
@@ -2155,8 +2177,10 @@
           <t>эскалация</t>
         </is>
       </c>
-      <c r="J38" t="n">
-        <v>0.067</v>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0.067</t>
+        </is>
       </c>
       <c r="K38" t="n">
         <v>150</v>
@@ -2206,8 +2230,10 @@
           <t>эскалация</t>
         </is>
       </c>
-      <c r="J39" t="n">
-        <v>0.007</v>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0.007</t>
+        </is>
       </c>
       <c r="K39" t="n">
         <v>150</v>
@@ -2257,8 +2283,10 @@
           <t>эскалация</t>
         </is>
       </c>
-      <c r="J40" t="n">
-        <v>0.073</v>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.073</t>
+        </is>
       </c>
       <c r="K40" t="n">
         <v>150</v>
@@ -2654,8 +2682,10 @@
           <t>эскалация</t>
         </is>
       </c>
-      <c r="J49" t="n">
-        <v>0.6</v>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
       </c>
       <c r="K49" t="n">
         <v>600</v>
@@ -2963,8 +2993,10 @@
           <t>тривиальный «всё уязвимо» F1</t>
         </is>
       </c>
-      <c r="J56" t="n">
-        <v>0.5</v>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
       </c>
       <c r="K56" t="n">
         <v>600</v>
@@ -3014,8 +3046,10 @@
           <t>нарушений бинарной инструкции</t>
         </is>
       </c>
-      <c r="J57" t="n">
-        <v>0</v>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K57" t="n">
         <v>600</v>
@@ -3065,8 +3099,10 @@
           <t>CWE accuracy</t>
         </is>
       </c>
-      <c r="J58" t="n">
-        <v>0.074</v>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>0.074</t>
+        </is>
       </c>
       <c r="K58" t="n">
         <v>600</v>
@@ -3116,8 +3152,10 @@
           <t>длина блока симв</t>
         </is>
       </c>
-      <c r="J59" t="n">
-        <v>0</v>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K59" t="n">
         <v>600</v>
@@ -3167,8 +3205,10 @@
           <t>длина блока симв</t>
         </is>
       </c>
-      <c r="J60" t="n">
-        <v>510</v>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
       </c>
       <c r="K60" t="n">
         <v>600</v>
@@ -3218,8 +3258,10 @@
           <t>длина блока симв</t>
         </is>
       </c>
-      <c r="J61" t="n">
-        <v>60</v>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="K61" t="n">
         <v>600</v>
@@ -3269,8 +3311,10 @@
           <t>длина блока симв</t>
         </is>
       </c>
-      <c r="J62" t="n">
-        <v>510</v>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
       </c>
       <c r="K62" t="n">
         <v>600</v>
@@ -3410,8 +3454,10 @@
           <t>утечка в train доля</t>
         </is>
       </c>
-      <c r="J65" t="n">
-        <v>0.378</v>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>0.378</t>
+        </is>
       </c>
       <c r="K65" t="n">
         <v>600</v>
@@ -3461,8 +3507,10 @@
           <t>утечка в train доля</t>
         </is>
       </c>
-      <c r="J66" t="n">
-        <v>0.378</v>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>0.378</t>
+        </is>
       </c>
       <c r="K66" t="n">
         <v>600</v>
@@ -3633,8 +3681,10 @@
           <t>доля попаданий (устоявшаяся)</t>
         </is>
       </c>
-      <c r="J70" t="n">
-        <v>0.454</v>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>0.454</t>
+        </is>
       </c>
       <c r="K70" t="n">
         <v>60</v>
@@ -3676,8 +3726,10 @@
           <t>доля попаданий (устоявшаяся)</t>
         </is>
       </c>
-      <c r="J71" t="n">
-        <v>0.725</v>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>0.725</t>
+        </is>
       </c>
       <c r="K71" t="n">
         <v>60</v>
@@ -3725,8 +3777,10 @@
           <t>кеш префикса (живой)</t>
         </is>
       </c>
-      <c r="J72" t="n">
-        <v>0.758</v>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>0.758</t>
+        </is>
       </c>
       <c r="K72" t="n">
         <v>200</v>
@@ -3774,8 +3828,10 @@
           <t>кеш префикса (живой)</t>
         </is>
       </c>
-      <c r="J73" t="n">
-        <v>0.758</v>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>0.758</t>
+        </is>
       </c>
       <c r="K73" t="n">
         <v>500</v>
@@ -3817,8 +3873,10 @@
           <t>вызовов LLM</t>
         </is>
       </c>
-      <c r="J74" t="n">
-        <v>480</v>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
       </c>
       <c r="K74" t="n">
         <v>10000</v>
@@ -3860,8 +3918,10 @@
           <t>доля vulnerable</t>
         </is>
       </c>
-      <c r="J75" t="n">
-        <v>0.1512</v>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>0.1512</t>
+        </is>
       </c>
       <c r="K75" t="n">
         <v>18864</v>
@@ -3903,8 +3963,10 @@
           <t>из них vulnerable</t>
         </is>
       </c>
-      <c r="J76" t="n">
-        <v>120</v>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
       </c>
       <c r="K76" t="n">
         <v>142</v>
@@ -3946,8 +4008,10 @@
           <t>док-в на ручную проверку</t>
         </is>
       </c>
-      <c r="J77" t="n">
-        <v>2067</v>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>2067</t>
+        </is>
       </c>
       <c r="K77" t="n">
         <v>100000</v>
@@ -3995,8 +4059,10 @@
           <t>recall без учёта типа</t>
         </is>
       </c>
-      <c r="J78" t="n">
-        <v>0.9088000000000001</v>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>0.9088</t>
+        </is>
       </c>
       <c r="K78" t="n">
         <v>100000</v>
@@ -4046,8 +4112,10 @@
           <t>MCC</t>
         </is>
       </c>
-      <c r="J79" t="n">
-        <v>0.9661</v>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>0.9661</t>
+        </is>
       </c>
       <c r="K79" t="n">
         <v>10000</v>
@@ -4097,8 +4165,10 @@
           <t>MCC</t>
         </is>
       </c>
-      <c r="J80" t="n">
-        <v>0.966</v>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>0.966</t>
+        </is>
       </c>
       <c r="K80" t="n">
         <v>10000</v>
@@ -4148,8 +4218,10 @@
           <t>Youden J</t>
         </is>
       </c>
-      <c r="J81" t="n">
-        <v>0.141</v>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>0.141</t>
+        </is>
       </c>
       <c r="K81" t="n">
         <v>18864</v>
@@ -4160,6 +4232,210 @@
       <c r="M81" t="inlineStr">
         <is>
           <t>J 0.141 против 0.140 на eval600 — различающая способность та же, F1 упал только от доли классов; тривиальное «всё vulnerable» даёт 0.1059</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>3</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>объединение слоёв (ПОСТАВКА)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>deepseek-chat + flawfinder + сигнатурный триаж</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>весь корпус, вердикт по объединению трёх слоёв</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0.1042</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.1637</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.1946</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Youden J</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>0.1874</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>18864</v>
+      </c>
+      <c r="L82" t="n">
+        <v>54679350</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>поставочная конфигурация; найдено 403 уязвимости против 300 у одной LLM; пересечение вместо объединения дало бы J +0.053 и 88 находок</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>3</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>базовая линия длины (НЕ сдаётся)</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>сортировка по len(code), бюджет 20.5% корпуса</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0.1259</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.4616</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.1979</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.1898</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Youden J</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>0.2718</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>18864</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>тривиальный признак обходит нашу конфигурацию; почти наверняка артефакт корпуса, в отчёт вынесен как честная базовая линия</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>3</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>semgrep r/c (ТУПИК)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>semgrep 1.175 реестр r/c</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>весь корпус, 16 правил для C</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0.1213</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.0701</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.08890000000000001</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Youden J</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>0.0400</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>18864</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>65.6% находок дублируют другие слои; из 210 уникальных уязвимых 11 при базе 5.6%; в объединении ухудшает J/F1/MCC</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>3</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>cppcheck (ТУПИК)</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>cppcheck 2.21</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>весь корпус, warning+style+portability</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>проверок безопасности</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>1 на 300</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>18864</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>16-22% фрагментов не разбираются (syntaxError); срабатывает только стилистика, её сигнал — артефакт длины (shadowVariable 3.25x -&gt; 0.84x с поправкой)</t>
         </is>
       </c>
     </row>
